--- a/Models/Данные по всем показателям wide.xlsx
+++ b/Models/Данные по всем показателям wide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Madi\ИВЦ БНС\Nowcasting\github 18082025\ICC\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002903B0-E037-4F47-BE6B-192230384C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55D4DC6-232B-434C-AEC5-C9E9F5BE1EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Верблюды" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="148">
   <si>
     <t>Период</t>
   </si>
@@ -456,6 +456,27 @@
   <si>
     <t>2024-12</t>
   </si>
+  <si>
+    <t>2025-01</t>
+  </si>
+  <si>
+    <t>2025-02</t>
+  </si>
+  <si>
+    <t>2025-03</t>
+  </si>
+  <si>
+    <t>2025-04</t>
+  </si>
+  <si>
+    <t>2025-05</t>
+  </si>
+  <si>
+    <t>2025-06</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
 </sst>
 </file>
 
@@ -818,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -7637,6 +7658,461 @@
       </c>
       <c r="U121">
         <v>764.43999999999994</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <v>129.30000000000001</v>
+      </c>
+      <c r="D122">
+        <v>22.6</v>
+      </c>
+      <c r="E122">
+        <v>322.10000000000002</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>109.8</v>
+      </c>
+      <c r="K122">
+        <v>2.5</v>
+      </c>
+      <c r="L122">
+        <v>0.4</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>450.07</v>
+      </c>
+      <c r="O122">
+        <v>164</v>
+      </c>
+      <c r="P122">
+        <v>5.25</v>
+      </c>
+      <c r="Q122">
+        <v>0</v>
+      </c>
+      <c r="R122">
+        <v>0</v>
+      </c>
+      <c r="S122">
+        <v>0</v>
+      </c>
+      <c r="T122">
+        <v>0</v>
+      </c>
+      <c r="U122">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+      <c r="C123">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="D123">
+        <v>19</v>
+      </c>
+      <c r="E123">
+        <v>286.54000000000002</v>
+      </c>
+      <c r="F123">
+        <v>0.7</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>36.4</v>
+      </c>
+      <c r="K123">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>376.72</v>
+      </c>
+      <c r="O123">
+        <v>580.5</v>
+      </c>
+      <c r="P123">
+        <v>1.4</v>
+      </c>
+      <c r="Q123">
+        <v>0.4</v>
+      </c>
+      <c r="R123">
+        <v>0</v>
+      </c>
+      <c r="S123">
+        <v>0</v>
+      </c>
+      <c r="T123">
+        <v>0</v>
+      </c>
+      <c r="U123">
+        <v>60.13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <v>411.5</v>
+      </c>
+      <c r="D124">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E124">
+        <v>447.4</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>60.4</v>
+      </c>
+      <c r="K124">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="L124">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>335.32</v>
+      </c>
+      <c r="O124">
+        <v>109.58</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R124">
+        <v>0</v>
+      </c>
+      <c r="S124">
+        <v>0</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124">
+        <v>93.1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>128.1</v>
+      </c>
+      <c r="D125">
+        <v>12</v>
+      </c>
+      <c r="E125">
+        <v>266.8</v>
+      </c>
+      <c r="F125">
+        <v>2.9</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>18.2</v>
+      </c>
+      <c r="K125">
+        <v>1.7</v>
+      </c>
+      <c r="L125">
+        <v>2</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>72.2</v>
+      </c>
+      <c r="O125">
+        <v>94.7</v>
+      </c>
+      <c r="P125">
+        <v>0.35</v>
+      </c>
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+      <c r="S125">
+        <v>0</v>
+      </c>
+      <c r="T125">
+        <v>0</v>
+      </c>
+      <c r="U125">
+        <v>85.800000000000011</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>235.7</v>
+      </c>
+      <c r="D126">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="E126">
+        <v>496.55</v>
+      </c>
+      <c r="F126">
+        <v>0.9</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>15.6</v>
+      </c>
+      <c r="K126">
+        <v>9.6</v>
+      </c>
+      <c r="L126">
+        <v>6.3</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>1.51</v>
+      </c>
+      <c r="O126">
+        <v>174.45</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+      <c r="S126">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126">
+        <v>96.610000000000014</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>12.2</v>
+      </c>
+      <c r="D127">
+        <v>41.599999999999987</v>
+      </c>
+      <c r="E127">
+        <v>688</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>19.7</v>
+      </c>
+      <c r="K127">
+        <v>59.92</v>
+      </c>
+      <c r="L127">
+        <v>6.4</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>56.94</v>
+      </c>
+      <c r="O127">
+        <v>317.85000000000002</v>
+      </c>
+      <c r="P127">
+        <v>3.98</v>
+      </c>
+      <c r="Q127">
+        <v>28.3</v>
+      </c>
+      <c r="R127">
+        <v>0</v>
+      </c>
+      <c r="S127">
+        <v>0</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+      <c r="U127">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>25.17</v>
+      </c>
+      <c r="D128">
+        <v>28.1</v>
+      </c>
+      <c r="E128">
+        <v>212.7</v>
+      </c>
+      <c r="F128">
+        <v>0.6</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>14.2</v>
+      </c>
+      <c r="K128">
+        <v>0.6</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>13.58</v>
+      </c>
+      <c r="O128">
+        <v>163.80000000000001</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>0</v>
+      </c>
+      <c r="R128">
+        <v>0</v>
+      </c>
+      <c r="S128">
+        <v>0</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128">
+        <v>44.099999999999987</v>
       </c>
     </row>
   </sheetData>
@@ -7646,7 +8122,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CE392EE-C88F-4826-BDAB-0FA3332DB2BC}">
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -14465,6 +14941,461 @@
       </c>
       <c r="U121">
         <v>29353.24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <v>3947.99</v>
+      </c>
+      <c r="C122">
+        <v>4466.24</v>
+      </c>
+      <c r="D122">
+        <v>2992.34</v>
+      </c>
+      <c r="E122">
+        <v>1583.87</v>
+      </c>
+      <c r="F122">
+        <v>1594.05</v>
+      </c>
+      <c r="G122">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H122">
+        <v>1.7</v>
+      </c>
+      <c r="I122">
+        <v>663.61</v>
+      </c>
+      <c r="J122">
+        <v>2386.42</v>
+      </c>
+      <c r="K122">
+        <v>2582.2600000000002</v>
+      </c>
+      <c r="L122">
+        <v>2251.02</v>
+      </c>
+      <c r="M122">
+        <v>2922.22</v>
+      </c>
+      <c r="N122">
+        <v>1341.74</v>
+      </c>
+      <c r="O122">
+        <v>99.240000000000009</v>
+      </c>
+      <c r="P122">
+        <v>1999.86</v>
+      </c>
+      <c r="Q122">
+        <v>2489.12</v>
+      </c>
+      <c r="R122">
+        <v>1319.15</v>
+      </c>
+      <c r="S122">
+        <v>2478.9</v>
+      </c>
+      <c r="T122">
+        <v>4007.77</v>
+      </c>
+      <c r="U122">
+        <v>8467.16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <v>3588.93</v>
+      </c>
+      <c r="C123">
+        <v>4548.2299999999996</v>
+      </c>
+      <c r="D123">
+        <v>2824.69</v>
+      </c>
+      <c r="E123">
+        <v>2020.86</v>
+      </c>
+      <c r="F123">
+        <v>2704.93</v>
+      </c>
+      <c r="G123">
+        <v>2.6</v>
+      </c>
+      <c r="H123">
+        <v>2.7</v>
+      </c>
+      <c r="I123">
+        <v>623.57000000000005</v>
+      </c>
+      <c r="J123">
+        <v>3163.3</v>
+      </c>
+      <c r="K123">
+        <v>3443.42</v>
+      </c>
+      <c r="L123">
+        <v>1655.31</v>
+      </c>
+      <c r="M123">
+        <v>3988.12</v>
+      </c>
+      <c r="N123">
+        <v>1075.3399999999999</v>
+      </c>
+      <c r="O123">
+        <v>132.08000000000001</v>
+      </c>
+      <c r="P123">
+        <v>2813.21</v>
+      </c>
+      <c r="Q123">
+        <v>1770.35</v>
+      </c>
+      <c r="R123">
+        <v>464.08</v>
+      </c>
+      <c r="S123">
+        <v>2439.4699999999998</v>
+      </c>
+      <c r="T123">
+        <v>2335.19</v>
+      </c>
+      <c r="U123">
+        <v>8032.34</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <v>4315.53</v>
+      </c>
+      <c r="C124">
+        <v>6574.41</v>
+      </c>
+      <c r="D124">
+        <v>8660.4500000000007</v>
+      </c>
+      <c r="E124">
+        <v>1740.22</v>
+      </c>
+      <c r="F124">
+        <v>2809.92</v>
+      </c>
+      <c r="G124">
+        <v>0.3</v>
+      </c>
+      <c r="H124">
+        <v>2.7</v>
+      </c>
+      <c r="I124">
+        <v>400.39</v>
+      </c>
+      <c r="J124">
+        <v>2715</v>
+      </c>
+      <c r="K124">
+        <v>4863.53</v>
+      </c>
+      <c r="L124">
+        <v>2404.2399999999998</v>
+      </c>
+      <c r="M124">
+        <v>3137.83</v>
+      </c>
+      <c r="N124">
+        <v>1109.6099999999999</v>
+      </c>
+      <c r="O124">
+        <v>103.05</v>
+      </c>
+      <c r="P124">
+        <v>3152.38</v>
+      </c>
+      <c r="Q124">
+        <v>7699.85</v>
+      </c>
+      <c r="R124">
+        <v>401.05</v>
+      </c>
+      <c r="S124">
+        <v>2864.2</v>
+      </c>
+      <c r="T124">
+        <v>2064.27</v>
+      </c>
+      <c r="U124">
+        <v>8225.02</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <v>3934.11</v>
+      </c>
+      <c r="C125">
+        <v>5766.3099999999986</v>
+      </c>
+      <c r="D125">
+        <v>2975.6</v>
+      </c>
+      <c r="E125">
+        <v>1429.08</v>
+      </c>
+      <c r="F125">
+        <v>2204.7600000000002</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>2</v>
+      </c>
+      <c r="I125">
+        <v>403.4</v>
+      </c>
+      <c r="J125">
+        <v>3245.04</v>
+      </c>
+      <c r="K125">
+        <v>3999.99</v>
+      </c>
+      <c r="L125">
+        <v>1792.75</v>
+      </c>
+      <c r="M125">
+        <v>3184.39</v>
+      </c>
+      <c r="N125">
+        <v>1429.88</v>
+      </c>
+      <c r="O125">
+        <v>279.48</v>
+      </c>
+      <c r="P125">
+        <v>2634.39</v>
+      </c>
+      <c r="Q125">
+        <v>2296.4299999999998</v>
+      </c>
+      <c r="R125">
+        <v>179.6</v>
+      </c>
+      <c r="S125">
+        <v>2872.67</v>
+      </c>
+      <c r="T125">
+        <v>1625.97</v>
+      </c>
+      <c r="U125">
+        <v>6628.2999999999993</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <v>3766.97</v>
+      </c>
+      <c r="C126">
+        <v>5446.24</v>
+      </c>
+      <c r="D126">
+        <v>4823.4399999999996</v>
+      </c>
+      <c r="E126">
+        <v>1686.36</v>
+      </c>
+      <c r="F126">
+        <v>2856.12</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>2.1</v>
+      </c>
+      <c r="I126">
+        <v>435.75</v>
+      </c>
+      <c r="J126">
+        <v>3464.3</v>
+      </c>
+      <c r="K126">
+        <v>4231.8600000000006</v>
+      </c>
+      <c r="L126">
+        <v>2202.71</v>
+      </c>
+      <c r="M126">
+        <v>4128.53</v>
+      </c>
+      <c r="N126">
+        <v>1463.98</v>
+      </c>
+      <c r="O126">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="P126">
+        <v>2757.33</v>
+      </c>
+      <c r="Q126">
+        <v>2733.24</v>
+      </c>
+      <c r="R126">
+        <v>443.45</v>
+      </c>
+      <c r="S126">
+        <v>2706.78</v>
+      </c>
+      <c r="T126">
+        <v>1849.39</v>
+      </c>
+      <c r="U126">
+        <v>7697.58</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <v>4346.53</v>
+      </c>
+      <c r="C127">
+        <v>7109.86</v>
+      </c>
+      <c r="D127">
+        <v>14601.52</v>
+      </c>
+      <c r="E127">
+        <v>1765.1</v>
+      </c>
+      <c r="F127">
+        <v>6147.46</v>
+      </c>
+      <c r="G127">
+        <v>45.5</v>
+      </c>
+      <c r="H127">
+        <v>2.6</v>
+      </c>
+      <c r="I127">
+        <v>517.70000000000005</v>
+      </c>
+      <c r="J127">
+        <v>6448.97</v>
+      </c>
+      <c r="K127">
+        <v>8235.66</v>
+      </c>
+      <c r="L127">
+        <v>6945.26</v>
+      </c>
+      <c r="M127">
+        <v>4248.12</v>
+      </c>
+      <c r="N127">
+        <v>1578.15</v>
+      </c>
+      <c r="O127">
+        <v>226</v>
+      </c>
+      <c r="P127">
+        <v>6965.91</v>
+      </c>
+      <c r="Q127">
+        <v>9527.94</v>
+      </c>
+      <c r="R127">
+        <v>854.7</v>
+      </c>
+      <c r="S127">
+        <v>4220.25</v>
+      </c>
+      <c r="T127">
+        <v>1416.17</v>
+      </c>
+      <c r="U127">
+        <v>9167.36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <v>2446.61</v>
+      </c>
+      <c r="C128">
+        <v>3555.44</v>
+      </c>
+      <c r="D128">
+        <v>2819.28</v>
+      </c>
+      <c r="E128">
+        <v>1007.1</v>
+      </c>
+      <c r="F128">
+        <v>3723.94</v>
+      </c>
+      <c r="G128">
+        <v>43.6</v>
+      </c>
+      <c r="H128">
+        <v>1.7</v>
+      </c>
+      <c r="I128">
+        <v>379.9</v>
+      </c>
+      <c r="J128">
+        <v>2419.61</v>
+      </c>
+      <c r="K128">
+        <v>3753.95</v>
+      </c>
+      <c r="L128">
+        <v>2125.5700000000002</v>
+      </c>
+      <c r="M128">
+        <v>1555.87</v>
+      </c>
+      <c r="N128">
+        <v>1481.05</v>
+      </c>
+      <c r="O128">
+        <v>98.66</v>
+      </c>
+      <c r="P128">
+        <v>2293.91</v>
+      </c>
+      <c r="Q128">
+        <v>1344.41</v>
+      </c>
+      <c r="R128">
+        <v>103.1</v>
+      </c>
+      <c r="S128">
+        <v>4780.7700000000004</v>
+      </c>
+      <c r="T128">
+        <v>2324.16</v>
+      </c>
+      <c r="U128">
+        <v>8580.2900000000009</v>
       </c>
     </row>
   </sheetData>
@@ -14474,7 +15405,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E85215AB-EA05-4143-A6D7-4B87D93E11F3}">
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -21293,6 +22224,461 @@
       </c>
       <c r="U121">
         <v>8733.5299999999988</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <v>1610.32</v>
+      </c>
+      <c r="C122">
+        <v>1632.1</v>
+      </c>
+      <c r="D122">
+        <v>549.47</v>
+      </c>
+      <c r="E122">
+        <v>555.20000000000005</v>
+      </c>
+      <c r="F122">
+        <v>694.36</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>5</v>
+      </c>
+      <c r="I122">
+        <v>86.1</v>
+      </c>
+      <c r="J122">
+        <v>1469.9</v>
+      </c>
+      <c r="K122">
+        <v>802.51</v>
+      </c>
+      <c r="L122">
+        <v>1336.21</v>
+      </c>
+      <c r="M122">
+        <v>391.11</v>
+      </c>
+      <c r="N122">
+        <v>821.5</v>
+      </c>
+      <c r="O122">
+        <v>90.899999999999991</v>
+      </c>
+      <c r="P122">
+        <v>1165.51</v>
+      </c>
+      <c r="Q122">
+        <v>1237.31</v>
+      </c>
+      <c r="R122">
+        <v>2126</v>
+      </c>
+      <c r="S122">
+        <v>1631.78</v>
+      </c>
+      <c r="T122">
+        <v>1080.05</v>
+      </c>
+      <c r="U122">
+        <v>2598.7600000000002</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <v>1067</v>
+      </c>
+      <c r="C123">
+        <v>834.44999999999993</v>
+      </c>
+      <c r="D123">
+        <v>727.18</v>
+      </c>
+      <c r="E123">
+        <v>934.8</v>
+      </c>
+      <c r="F123">
+        <v>910.63000000000011</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>1.6</v>
+      </c>
+      <c r="I123">
+        <v>60.7</v>
+      </c>
+      <c r="J123">
+        <v>903.7</v>
+      </c>
+      <c r="K123">
+        <v>900.05</v>
+      </c>
+      <c r="L123">
+        <v>779.29</v>
+      </c>
+      <c r="M123">
+        <v>263.5</v>
+      </c>
+      <c r="N123">
+        <v>819.07</v>
+      </c>
+      <c r="O123">
+        <v>123.95</v>
+      </c>
+      <c r="P123">
+        <v>1732.91</v>
+      </c>
+      <c r="Q123">
+        <v>1032.43</v>
+      </c>
+      <c r="R123">
+        <v>413.5</v>
+      </c>
+      <c r="S123">
+        <v>1565.58</v>
+      </c>
+      <c r="T123">
+        <v>307.14999999999998</v>
+      </c>
+      <c r="U123">
+        <v>2732.23</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <v>1190.29</v>
+      </c>
+      <c r="C124">
+        <v>1715.21</v>
+      </c>
+      <c r="D124">
+        <v>3248.83</v>
+      </c>
+      <c r="E124">
+        <v>877.25</v>
+      </c>
+      <c r="F124">
+        <v>592.57000000000005</v>
+      </c>
+      <c r="G124">
+        <v>0.4</v>
+      </c>
+      <c r="H124">
+        <v>3.6</v>
+      </c>
+      <c r="I124">
+        <v>46.8</v>
+      </c>
+      <c r="J124">
+        <v>1540.2</v>
+      </c>
+      <c r="K124">
+        <v>1034.46</v>
+      </c>
+      <c r="L124">
+        <v>1358.98</v>
+      </c>
+      <c r="M124">
+        <v>366.41</v>
+      </c>
+      <c r="N124">
+        <v>758.66000000000008</v>
+      </c>
+      <c r="O124">
+        <v>205.05</v>
+      </c>
+      <c r="P124">
+        <v>2347.5100000000002</v>
+      </c>
+      <c r="Q124">
+        <v>1470.26</v>
+      </c>
+      <c r="R124">
+        <v>795.30000000000007</v>
+      </c>
+      <c r="S124">
+        <v>1804.74</v>
+      </c>
+      <c r="T124">
+        <v>569.04999999999995</v>
+      </c>
+      <c r="U124">
+        <v>2726.66</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <v>936.81999999999994</v>
+      </c>
+      <c r="C125">
+        <v>1757.48</v>
+      </c>
+      <c r="D125">
+        <v>978.78</v>
+      </c>
+      <c r="E125">
+        <v>667.5</v>
+      </c>
+      <c r="F125">
+        <v>1041.58</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I125">
+        <v>44.4</v>
+      </c>
+      <c r="J125">
+        <v>962.22</v>
+      </c>
+      <c r="K125">
+        <v>1049.5899999999999</v>
+      </c>
+      <c r="L125">
+        <v>1678.28</v>
+      </c>
+      <c r="M125">
+        <v>216.41</v>
+      </c>
+      <c r="N125">
+        <v>872.49</v>
+      </c>
+      <c r="O125">
+        <v>131.6</v>
+      </c>
+      <c r="P125">
+        <v>2583.73</v>
+      </c>
+      <c r="Q125">
+        <v>386.71</v>
+      </c>
+      <c r="R125">
+        <v>373.6</v>
+      </c>
+      <c r="S125">
+        <v>1533.22</v>
+      </c>
+      <c r="T125">
+        <v>522.74</v>
+      </c>
+      <c r="U125">
+        <v>2579.69</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <v>1068.99</v>
+      </c>
+      <c r="C126">
+        <v>1457.7</v>
+      </c>
+      <c r="D126">
+        <v>787.7</v>
+      </c>
+      <c r="E126">
+        <v>1008.2</v>
+      </c>
+      <c r="F126">
+        <v>1239.3599999999999</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>1.8</v>
+      </c>
+      <c r="I126">
+        <v>35.5</v>
+      </c>
+      <c r="J126">
+        <v>1525.3</v>
+      </c>
+      <c r="K126">
+        <v>1000.72</v>
+      </c>
+      <c r="L126">
+        <v>1322.31</v>
+      </c>
+      <c r="M126">
+        <v>1214.1600000000001</v>
+      </c>
+      <c r="N126">
+        <v>578.73</v>
+      </c>
+      <c r="O126">
+        <v>193.7</v>
+      </c>
+      <c r="P126">
+        <v>3180.08</v>
+      </c>
+      <c r="Q126">
+        <v>372.01</v>
+      </c>
+      <c r="R126">
+        <v>415.8</v>
+      </c>
+      <c r="S126">
+        <v>1589.3</v>
+      </c>
+      <c r="T126">
+        <v>506.27</v>
+      </c>
+      <c r="U126">
+        <v>1902.11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <v>2008.72</v>
+      </c>
+      <c r="C127">
+        <v>2493.35</v>
+      </c>
+      <c r="D127">
+        <v>2309.5</v>
+      </c>
+      <c r="E127">
+        <v>720.25</v>
+      </c>
+      <c r="F127">
+        <v>2347.63</v>
+      </c>
+      <c r="G127">
+        <v>1.5</v>
+      </c>
+      <c r="H127">
+        <v>1.8</v>
+      </c>
+      <c r="I127">
+        <v>38.6</v>
+      </c>
+      <c r="J127">
+        <v>2182.3000000000002</v>
+      </c>
+      <c r="K127">
+        <v>1661.76</v>
+      </c>
+      <c r="L127">
+        <v>3725.33</v>
+      </c>
+      <c r="M127">
+        <v>1154.83</v>
+      </c>
+      <c r="N127">
+        <v>1190.92</v>
+      </c>
+      <c r="O127">
+        <v>305.8</v>
+      </c>
+      <c r="P127">
+        <v>5805.7</v>
+      </c>
+      <c r="Q127">
+        <v>3180.35</v>
+      </c>
+      <c r="R127">
+        <v>1513.7</v>
+      </c>
+      <c r="S127">
+        <v>3332.59</v>
+      </c>
+      <c r="T127">
+        <v>1524.19</v>
+      </c>
+      <c r="U127">
+        <v>2208.35</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <v>1050.06</v>
+      </c>
+      <c r="C128">
+        <v>1468.96</v>
+      </c>
+      <c r="D128">
+        <v>910.76</v>
+      </c>
+      <c r="E128">
+        <v>492.30000000000013</v>
+      </c>
+      <c r="F128">
+        <v>1570.65</v>
+      </c>
+      <c r="G128">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H128">
+        <v>0.6</v>
+      </c>
+      <c r="I128">
+        <v>49.2</v>
+      </c>
+      <c r="J128">
+        <v>646.79999999999995</v>
+      </c>
+      <c r="K128">
+        <v>642.32000000000005</v>
+      </c>
+      <c r="L128">
+        <v>873.83999999999992</v>
+      </c>
+      <c r="M128">
+        <v>250.09</v>
+      </c>
+      <c r="N128">
+        <v>1070.6600000000001</v>
+      </c>
+      <c r="O128">
+        <v>159.6</v>
+      </c>
+      <c r="P128">
+        <v>6077.3</v>
+      </c>
+      <c r="Q128">
+        <v>264.57</v>
+      </c>
+      <c r="R128">
+        <v>751.7</v>
+      </c>
+      <c r="S128">
+        <v>2325.81</v>
+      </c>
+      <c r="T128">
+        <v>2030.74</v>
+      </c>
+      <c r="U128">
+        <v>2272.7399999999998</v>
       </c>
     </row>
   </sheetData>
@@ -21302,7 +22688,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76ECE8AE-1027-42BD-B507-CDDAB72739F4}">
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -28121,6 +29507,461 @@
       </c>
       <c r="U121">
         <v>28616.799999999999</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <v>11378.1</v>
+      </c>
+      <c r="C122">
+        <v>3645.1</v>
+      </c>
+      <c r="D122">
+        <v>18568.900000000001</v>
+      </c>
+      <c r="E122">
+        <v>1102.5999999999999</v>
+      </c>
+      <c r="F122">
+        <v>11925.9</v>
+      </c>
+      <c r="G122">
+        <v>24.9</v>
+      </c>
+      <c r="H122">
+        <v>6.6</v>
+      </c>
+      <c r="I122">
+        <v>4112</v>
+      </c>
+      <c r="J122">
+        <v>11870.5</v>
+      </c>
+      <c r="K122">
+        <v>3211.2</v>
+      </c>
+      <c r="L122">
+        <v>4413.5</v>
+      </c>
+      <c r="M122">
+        <v>12296.7</v>
+      </c>
+      <c r="N122">
+        <v>3000.2</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>9509.7999999999993</v>
+      </c>
+      <c r="Q122">
+        <v>10947.2</v>
+      </c>
+      <c r="R122">
+        <v>943.59999999999991</v>
+      </c>
+      <c r="S122">
+        <v>15361.5</v>
+      </c>
+      <c r="T122">
+        <v>17844.5</v>
+      </c>
+      <c r="U122">
+        <v>33158</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <v>12075.2</v>
+      </c>
+      <c r="C123">
+        <v>7802.9</v>
+      </c>
+      <c r="D123">
+        <v>16396.400000000001</v>
+      </c>
+      <c r="E123">
+        <v>1147.4000000000001</v>
+      </c>
+      <c r="F123">
+        <v>13309</v>
+      </c>
+      <c r="G123">
+        <v>25.7</v>
+      </c>
+      <c r="H123">
+        <v>6.3</v>
+      </c>
+      <c r="I123">
+        <v>4463.5</v>
+      </c>
+      <c r="J123">
+        <v>11950.3</v>
+      </c>
+      <c r="K123">
+        <v>6609.1</v>
+      </c>
+      <c r="L123">
+        <v>7045.2</v>
+      </c>
+      <c r="M123">
+        <v>14608.5</v>
+      </c>
+      <c r="N123">
+        <v>3036.2</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>12638.2</v>
+      </c>
+      <c r="Q123">
+        <v>9818</v>
+      </c>
+      <c r="R123">
+        <v>2536.8000000000002</v>
+      </c>
+      <c r="S123">
+        <v>15701.3</v>
+      </c>
+      <c r="T123">
+        <v>18781.599999999999</v>
+      </c>
+      <c r="U123">
+        <v>35623.699999999997</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <v>18113.7</v>
+      </c>
+      <c r="C124">
+        <v>14584.2</v>
+      </c>
+      <c r="D124">
+        <v>20150.5</v>
+      </c>
+      <c r="E124">
+        <v>1787.2</v>
+      </c>
+      <c r="F124">
+        <v>17781.5</v>
+      </c>
+      <c r="G124">
+        <v>25.1</v>
+      </c>
+      <c r="H124">
+        <v>6.8</v>
+      </c>
+      <c r="I124">
+        <v>5183.2000000000007</v>
+      </c>
+      <c r="J124">
+        <v>12804.8</v>
+      </c>
+      <c r="K124">
+        <v>9067.2999999999993</v>
+      </c>
+      <c r="L124">
+        <v>16438.5</v>
+      </c>
+      <c r="M124">
+        <v>15571.1</v>
+      </c>
+      <c r="N124">
+        <v>3195.7</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>20932.400000000001</v>
+      </c>
+      <c r="Q124">
+        <v>16812.400000000001</v>
+      </c>
+      <c r="R124">
+        <v>4311.8999999999996</v>
+      </c>
+      <c r="S124">
+        <v>19059</v>
+      </c>
+      <c r="T124">
+        <v>22952.799999999999</v>
+      </c>
+      <c r="U124">
+        <v>44086.400000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <v>20536.099999999999</v>
+      </c>
+      <c r="C125">
+        <v>12551</v>
+      </c>
+      <c r="D125">
+        <v>19816.5</v>
+      </c>
+      <c r="E125">
+        <v>2839.9</v>
+      </c>
+      <c r="F125">
+        <v>21818.7</v>
+      </c>
+      <c r="G125">
+        <v>27.8</v>
+      </c>
+      <c r="H125">
+        <v>11.8</v>
+      </c>
+      <c r="I125">
+        <v>6926.2000000000007</v>
+      </c>
+      <c r="J125">
+        <v>20325.3</v>
+      </c>
+      <c r="K125">
+        <v>19342.5</v>
+      </c>
+      <c r="L125">
+        <v>16593.3</v>
+      </c>
+      <c r="M125">
+        <v>25665.200000000001</v>
+      </c>
+      <c r="N125">
+        <v>3601.1</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>26104.5</v>
+      </c>
+      <c r="Q125">
+        <v>19826.099999999999</v>
+      </c>
+      <c r="R125">
+        <v>5524.8</v>
+      </c>
+      <c r="S125">
+        <v>21595.3</v>
+      </c>
+      <c r="T125">
+        <v>34340.300000000003</v>
+      </c>
+      <c r="U125">
+        <v>49990.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <v>24905.7</v>
+      </c>
+      <c r="C126">
+        <v>15396.2</v>
+      </c>
+      <c r="D126">
+        <v>23213</v>
+      </c>
+      <c r="E126">
+        <v>5432.7</v>
+      </c>
+      <c r="F126">
+        <v>24180</v>
+      </c>
+      <c r="G126">
+        <v>29.8</v>
+      </c>
+      <c r="H126">
+        <v>10.8</v>
+      </c>
+      <c r="I126">
+        <v>7755.3</v>
+      </c>
+      <c r="J126">
+        <v>21966.6</v>
+      </c>
+      <c r="K126">
+        <v>35421.800000000003</v>
+      </c>
+      <c r="L126">
+        <v>25008.400000000001</v>
+      </c>
+      <c r="M126">
+        <v>24862.799999999999</v>
+      </c>
+      <c r="N126">
+        <v>3887.4</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>30026.3</v>
+      </c>
+      <c r="Q126">
+        <v>19147.2</v>
+      </c>
+      <c r="R126">
+        <v>7606.2999999999993</v>
+      </c>
+      <c r="S126">
+        <v>23858.2</v>
+      </c>
+      <c r="T126">
+        <v>38714.800000000003</v>
+      </c>
+      <c r="U126">
+        <v>59303.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <v>28491.599999999999</v>
+      </c>
+      <c r="C127">
+        <v>26838.1</v>
+      </c>
+      <c r="D127">
+        <v>33260.5</v>
+      </c>
+      <c r="E127">
+        <v>4032.2</v>
+      </c>
+      <c r="F127">
+        <v>30155.4</v>
+      </c>
+      <c r="G127">
+        <v>27.9</v>
+      </c>
+      <c r="H127">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="I127">
+        <v>8152.1</v>
+      </c>
+      <c r="J127">
+        <v>29428.1</v>
+      </c>
+      <c r="K127">
+        <v>40245.9</v>
+      </c>
+      <c r="L127">
+        <v>33051.300000000003</v>
+      </c>
+      <c r="M127">
+        <v>48355.4</v>
+      </c>
+      <c r="N127">
+        <v>4754.3</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>43388.800000000003</v>
+      </c>
+      <c r="Q127">
+        <v>27639</v>
+      </c>
+      <c r="R127">
+        <v>5966.7</v>
+      </c>
+      <c r="S127">
+        <v>29471.7</v>
+      </c>
+      <c r="T127">
+        <v>45201.5</v>
+      </c>
+      <c r="U127">
+        <v>61702.9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <v>25379.9</v>
+      </c>
+      <c r="C128">
+        <v>22505.1</v>
+      </c>
+      <c r="D128">
+        <v>31438.9</v>
+      </c>
+      <c r="E128">
+        <v>2987.3</v>
+      </c>
+      <c r="F128">
+        <v>28246.7</v>
+      </c>
+      <c r="G128">
+        <v>27.1</v>
+      </c>
+      <c r="H128">
+        <v>21.4</v>
+      </c>
+      <c r="I128">
+        <v>6931.2</v>
+      </c>
+      <c r="J128">
+        <v>22638.400000000001</v>
+      </c>
+      <c r="K128">
+        <v>28134.5</v>
+      </c>
+      <c r="L128">
+        <v>22114.3</v>
+      </c>
+      <c r="M128">
+        <v>24434.400000000001</v>
+      </c>
+      <c r="N128">
+        <v>4682.8999999999996</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>37435.4</v>
+      </c>
+      <c r="Q128">
+        <v>21703.200000000001</v>
+      </c>
+      <c r="R128">
+        <v>10042.5</v>
+      </c>
+      <c r="S128">
+        <v>28373.200000000001</v>
+      </c>
+      <c r="T128">
+        <v>46680.7</v>
+      </c>
+      <c r="U128">
+        <v>43495.5</v>
       </c>
     </row>
   </sheetData>
@@ -28130,7 +29971,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D340951-7ACF-4DE8-BFB4-03C678D869C4}">
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -34949,6 +36790,461 @@
       </c>
       <c r="U121">
         <v>8866.36</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <v>606.55999999999995</v>
+      </c>
+      <c r="C122">
+        <v>1267.28</v>
+      </c>
+      <c r="D122">
+        <v>1113.56</v>
+      </c>
+      <c r="E122">
+        <v>488.55000000000013</v>
+      </c>
+      <c r="F122">
+        <v>516.73</v>
+      </c>
+      <c r="G122">
+        <v>0.6</v>
+      </c>
+      <c r="H122">
+        <v>0.7</v>
+      </c>
+      <c r="I122">
+        <v>108.39</v>
+      </c>
+      <c r="J122">
+        <v>1880.47</v>
+      </c>
+      <c r="K122">
+        <v>595.67000000000007</v>
+      </c>
+      <c r="L122">
+        <v>381</v>
+      </c>
+      <c r="M122">
+        <v>330.86</v>
+      </c>
+      <c r="N122">
+        <v>533.78</v>
+      </c>
+      <c r="O122">
+        <v>151.54</v>
+      </c>
+      <c r="P122">
+        <v>612.23</v>
+      </c>
+      <c r="Q122">
+        <v>689.58</v>
+      </c>
+      <c r="R122">
+        <v>338.6</v>
+      </c>
+      <c r="S122">
+        <v>392.03</v>
+      </c>
+      <c r="T122">
+        <v>328.67</v>
+      </c>
+      <c r="U122">
+        <v>4447.97</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <v>807.76</v>
+      </c>
+      <c r="C123">
+        <v>536.79</v>
+      </c>
+      <c r="D123">
+        <v>526.89</v>
+      </c>
+      <c r="E123">
+        <v>574.59999999999991</v>
+      </c>
+      <c r="F123">
+        <v>716.8</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0.7</v>
+      </c>
+      <c r="I123">
+        <v>76.72</v>
+      </c>
+      <c r="J123">
+        <v>1806.25</v>
+      </c>
+      <c r="K123">
+        <v>629.36</v>
+      </c>
+      <c r="L123">
+        <v>375.04</v>
+      </c>
+      <c r="M123">
+        <v>141.87</v>
+      </c>
+      <c r="N123">
+        <v>474.22</v>
+      </c>
+      <c r="O123">
+        <v>157.54</v>
+      </c>
+      <c r="P123">
+        <v>873.94999999999993</v>
+      </c>
+      <c r="Q123">
+        <v>634.30999999999995</v>
+      </c>
+      <c r="R123">
+        <v>294.8</v>
+      </c>
+      <c r="S123">
+        <v>423.63</v>
+      </c>
+      <c r="T123">
+        <v>73.459999999999994</v>
+      </c>
+      <c r="U123">
+        <v>4266.88</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <v>799.68</v>
+      </c>
+      <c r="C124">
+        <v>2929.62</v>
+      </c>
+      <c r="D124">
+        <v>3722.4</v>
+      </c>
+      <c r="E124">
+        <v>986.82999999999993</v>
+      </c>
+      <c r="F124">
+        <v>1048.98</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>1.2</v>
+      </c>
+      <c r="I124">
+        <v>63.56</v>
+      </c>
+      <c r="J124">
+        <v>2109.5</v>
+      </c>
+      <c r="K124">
+        <v>1093.1300000000001</v>
+      </c>
+      <c r="L124">
+        <v>837.54</v>
+      </c>
+      <c r="M124">
+        <v>179.06</v>
+      </c>
+      <c r="N124">
+        <v>443.29</v>
+      </c>
+      <c r="O124">
+        <v>131.34</v>
+      </c>
+      <c r="P124">
+        <v>1305.68</v>
+      </c>
+      <c r="Q124">
+        <v>3323.46</v>
+      </c>
+      <c r="R124">
+        <v>306.89999999999998</v>
+      </c>
+      <c r="S124">
+        <v>527.44000000000005</v>
+      </c>
+      <c r="T124">
+        <v>226.5</v>
+      </c>
+      <c r="U124">
+        <v>4540.22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <v>798.4</v>
+      </c>
+      <c r="C125">
+        <v>1795.06</v>
+      </c>
+      <c r="D125">
+        <v>775.32999999999993</v>
+      </c>
+      <c r="E125">
+        <v>812.85</v>
+      </c>
+      <c r="F125">
+        <v>832.48</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0.8</v>
+      </c>
+      <c r="I125">
+        <v>49.8</v>
+      </c>
+      <c r="J125">
+        <v>2102.1</v>
+      </c>
+      <c r="K125">
+        <v>1348</v>
+      </c>
+      <c r="L125">
+        <v>357.73</v>
+      </c>
+      <c r="M125">
+        <v>1433.99</v>
+      </c>
+      <c r="N125">
+        <v>309.81</v>
+      </c>
+      <c r="O125">
+        <v>51.12</v>
+      </c>
+      <c r="P125">
+        <v>1741.28</v>
+      </c>
+      <c r="Q125">
+        <v>811.68000000000006</v>
+      </c>
+      <c r="R125">
+        <v>261.8</v>
+      </c>
+      <c r="S125">
+        <v>904.24</v>
+      </c>
+      <c r="T125">
+        <v>324.2</v>
+      </c>
+      <c r="U125">
+        <v>3939.72</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <v>819.94999999999993</v>
+      </c>
+      <c r="C126">
+        <v>1235.48</v>
+      </c>
+      <c r="D126">
+        <v>937.06</v>
+      </c>
+      <c r="E126">
+        <v>755.93000000000006</v>
+      </c>
+      <c r="F126">
+        <v>946.63</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0.9</v>
+      </c>
+      <c r="I126">
+        <v>48</v>
+      </c>
+      <c r="J126">
+        <v>2455.4</v>
+      </c>
+      <c r="K126">
+        <v>1610.72</v>
+      </c>
+      <c r="L126">
+        <v>1127.95</v>
+      </c>
+      <c r="M126">
+        <v>149.31</v>
+      </c>
+      <c r="N126">
+        <v>628.26</v>
+      </c>
+      <c r="O126">
+        <v>132.38999999999999</v>
+      </c>
+      <c r="P126">
+        <v>2006.25</v>
+      </c>
+      <c r="Q126">
+        <v>643.79999999999995</v>
+      </c>
+      <c r="R126">
+        <v>699</v>
+      </c>
+      <c r="S126">
+        <v>819.04</v>
+      </c>
+      <c r="T126">
+        <v>431.65</v>
+      </c>
+      <c r="U126">
+        <v>3631.9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <v>909.79</v>
+      </c>
+      <c r="C127">
+        <v>2052.14</v>
+      </c>
+      <c r="D127">
+        <v>3243.32</v>
+      </c>
+      <c r="E127">
+        <v>2961.75</v>
+      </c>
+      <c r="F127">
+        <v>1415.91</v>
+      </c>
+      <c r="G127">
+        <v>5</v>
+      </c>
+      <c r="H127">
+        <v>0.7</v>
+      </c>
+      <c r="I127">
+        <v>85.1</v>
+      </c>
+      <c r="J127">
+        <v>4804</v>
+      </c>
+      <c r="K127">
+        <v>2238.4699999999998</v>
+      </c>
+      <c r="L127">
+        <v>2110.63</v>
+      </c>
+      <c r="M127">
+        <v>133.91999999999999</v>
+      </c>
+      <c r="N127">
+        <v>526.67999999999995</v>
+      </c>
+      <c r="O127">
+        <v>207.71</v>
+      </c>
+      <c r="P127">
+        <v>4668.04</v>
+      </c>
+      <c r="Q127">
+        <v>4021.84</v>
+      </c>
+      <c r="R127">
+        <v>794.2</v>
+      </c>
+      <c r="S127">
+        <v>1158.24</v>
+      </c>
+      <c r="T127">
+        <v>492.27</v>
+      </c>
+      <c r="U127">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <v>525.54</v>
+      </c>
+      <c r="C128">
+        <v>1244.06</v>
+      </c>
+      <c r="D128">
+        <v>950.93000000000006</v>
+      </c>
+      <c r="E128">
+        <v>744.45</v>
+      </c>
+      <c r="F128">
+        <v>1527.06</v>
+      </c>
+      <c r="G128">
+        <v>6</v>
+      </c>
+      <c r="H128">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I128">
+        <v>128.01</v>
+      </c>
+      <c r="J128">
+        <v>2430.85</v>
+      </c>
+      <c r="K128">
+        <v>1548.44</v>
+      </c>
+      <c r="L128">
+        <v>518.04999999999995</v>
+      </c>
+      <c r="M128">
+        <v>153.09</v>
+      </c>
+      <c r="N128">
+        <v>250.73</v>
+      </c>
+      <c r="O128">
+        <v>176.88</v>
+      </c>
+      <c r="P128">
+        <v>1030.78</v>
+      </c>
+      <c r="Q128">
+        <v>801.79000000000008</v>
+      </c>
+      <c r="R128">
+        <v>246.9</v>
+      </c>
+      <c r="S128">
+        <v>573.29999999999995</v>
+      </c>
+      <c r="T128">
+        <v>989.64</v>
+      </c>
+      <c r="U128">
+        <v>2576.4699999999998</v>
       </c>
     </row>
   </sheetData>
@@ -34958,7 +37254,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF3FD1C-DB44-43BF-AC6D-60EBCBF6A679}">
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -41777,6 +44073,461 @@
       </c>
       <c r="U121">
         <v>565.34</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <v>8560.2999999999993</v>
+      </c>
+      <c r="C122">
+        <v>54.3</v>
+      </c>
+      <c r="D122">
+        <v>12023.33</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>6376.96</v>
+      </c>
+      <c r="G122">
+        <v>0.1</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>3.8</v>
+      </c>
+      <c r="J122">
+        <v>1983.67</v>
+      </c>
+      <c r="K122">
+        <v>972.64</v>
+      </c>
+      <c r="L122">
+        <v>1000.83</v>
+      </c>
+      <c r="M122">
+        <v>1481.59</v>
+      </c>
+      <c r="N122">
+        <v>1.4</v>
+      </c>
+      <c r="O122">
+        <v>508.83</v>
+      </c>
+      <c r="P122">
+        <v>1879.2</v>
+      </c>
+      <c r="Q122">
+        <v>279.8</v>
+      </c>
+      <c r="R122">
+        <v>0</v>
+      </c>
+      <c r="S122">
+        <v>319.17</v>
+      </c>
+      <c r="T122">
+        <v>414.05000000000013</v>
+      </c>
+      <c r="U122">
+        <v>810.6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <v>12551.51</v>
+      </c>
+      <c r="C123">
+        <v>30.5</v>
+      </c>
+      <c r="D123">
+        <v>10821.1</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>5574.8099999999986</v>
+      </c>
+      <c r="G123">
+        <v>0.1</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="J123">
+        <v>1817.65</v>
+      </c>
+      <c r="K123">
+        <v>1047.8800000000001</v>
+      </c>
+      <c r="L123">
+        <v>892.11</v>
+      </c>
+      <c r="M123">
+        <v>1377.83</v>
+      </c>
+      <c r="N123">
+        <v>10.95</v>
+      </c>
+      <c r="O123">
+        <v>427.6</v>
+      </c>
+      <c r="P123">
+        <v>1683.5</v>
+      </c>
+      <c r="Q123">
+        <v>3.9</v>
+      </c>
+      <c r="R123">
+        <v>0</v>
+      </c>
+      <c r="S123">
+        <v>252.85</v>
+      </c>
+      <c r="T123">
+        <v>496.82</v>
+      </c>
+      <c r="U123">
+        <v>641.64</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <v>12385.3</v>
+      </c>
+      <c r="C124">
+        <v>18</v>
+      </c>
+      <c r="D124">
+        <v>12752.96</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>6469.33</v>
+      </c>
+      <c r="G124">
+        <v>0.1</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>2.7</v>
+      </c>
+      <c r="J124">
+        <v>2596.0700000000002</v>
+      </c>
+      <c r="K124">
+        <v>1179.17</v>
+      </c>
+      <c r="L124">
+        <v>877.74000000000012</v>
+      </c>
+      <c r="M124">
+        <v>1435.98</v>
+      </c>
+      <c r="N124">
+        <v>5.3</v>
+      </c>
+      <c r="O124">
+        <v>618.79999999999995</v>
+      </c>
+      <c r="P124">
+        <v>1821.7</v>
+      </c>
+      <c r="Q124">
+        <v>5.9</v>
+      </c>
+      <c r="R124">
+        <v>0</v>
+      </c>
+      <c r="S124">
+        <v>234.53</v>
+      </c>
+      <c r="T124">
+        <v>705.66</v>
+      </c>
+      <c r="U124">
+        <v>802.30000000000007</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <v>13015.9</v>
+      </c>
+      <c r="C125">
+        <v>48.6</v>
+      </c>
+      <c r="D125">
+        <v>13346.82</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>6486.09</v>
+      </c>
+      <c r="G125">
+        <v>0.1</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>4.8</v>
+      </c>
+      <c r="J125">
+        <v>1968.29</v>
+      </c>
+      <c r="K125">
+        <v>989.24</v>
+      </c>
+      <c r="L125">
+        <v>1046.8</v>
+      </c>
+      <c r="M125">
+        <v>1111.97</v>
+      </c>
+      <c r="N125">
+        <v>5.6000000000000014</v>
+      </c>
+      <c r="O125">
+        <v>1039.8800000000001</v>
+      </c>
+      <c r="P125">
+        <v>2239.8000000000002</v>
+      </c>
+      <c r="Q125">
+        <v>124.4</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+      <c r="S125">
+        <v>559.95000000000005</v>
+      </c>
+      <c r="T125">
+        <v>574.51</v>
+      </c>
+      <c r="U125">
+        <v>750.07</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <v>10609</v>
+      </c>
+      <c r="C126">
+        <v>23.9</v>
+      </c>
+      <c r="D126">
+        <v>11619.21</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>6221.83</v>
+      </c>
+      <c r="G126">
+        <v>0.1</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>3.6</v>
+      </c>
+      <c r="J126">
+        <v>1939.64</v>
+      </c>
+      <c r="K126">
+        <v>1101.94</v>
+      </c>
+      <c r="L126">
+        <v>920.13000000000011</v>
+      </c>
+      <c r="M126">
+        <v>1062.9100000000001</v>
+      </c>
+      <c r="N126">
+        <v>3.5</v>
+      </c>
+      <c r="O126">
+        <v>730.33</v>
+      </c>
+      <c r="P126">
+        <v>2224.6999999999998</v>
+      </c>
+      <c r="Q126">
+        <v>280.2</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+      <c r="S126">
+        <v>564.42999999999995</v>
+      </c>
+      <c r="T126">
+        <v>682.0100000000001</v>
+      </c>
+      <c r="U126">
+        <v>754.31</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <v>10408.6</v>
+      </c>
+      <c r="C127">
+        <v>52.4</v>
+      </c>
+      <c r="D127">
+        <v>10505.14</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>6069.3099999999986</v>
+      </c>
+      <c r="G127">
+        <v>0.1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>4.3</v>
+      </c>
+      <c r="J127">
+        <v>1631.96</v>
+      </c>
+      <c r="K127">
+        <v>1008.55</v>
+      </c>
+      <c r="L127">
+        <v>1090.8900000000001</v>
+      </c>
+      <c r="M127">
+        <v>988.78</v>
+      </c>
+      <c r="N127">
+        <v>7.9</v>
+      </c>
+      <c r="O127">
+        <v>876.72</v>
+      </c>
+      <c r="P127">
+        <v>1720.7</v>
+      </c>
+      <c r="Q127">
+        <v>175.8</v>
+      </c>
+      <c r="R127">
+        <v>0</v>
+      </c>
+      <c r="S127">
+        <v>819.95999999999992</v>
+      </c>
+      <c r="T127">
+        <v>730.13</v>
+      </c>
+      <c r="U127">
+        <v>925.67000000000007</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <v>10639.7</v>
+      </c>
+      <c r="C128">
+        <v>60.6</v>
+      </c>
+      <c r="D128">
+        <v>10844.25</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>6186.68</v>
+      </c>
+      <c r="G128">
+        <v>0.1</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>4</v>
+      </c>
+      <c r="J128">
+        <v>1759.46</v>
+      </c>
+      <c r="K128">
+        <v>912.93000000000006</v>
+      </c>
+      <c r="L128">
+        <v>866.56999999999994</v>
+      </c>
+      <c r="M128">
+        <v>1083.18</v>
+      </c>
+      <c r="N128">
+        <v>0.3</v>
+      </c>
+      <c r="O128">
+        <v>911.41</v>
+      </c>
+      <c r="P128">
+        <v>2036.8</v>
+      </c>
+      <c r="Q128">
+        <v>26.8</v>
+      </c>
+      <c r="R128">
+        <v>9.5</v>
+      </c>
+      <c r="S128">
+        <v>914.28000000000009</v>
+      </c>
+      <c r="T128">
+        <v>978.55000000000007</v>
+      </c>
+      <c r="U128">
+        <v>627.59999999999991</v>
       </c>
     </row>
   </sheetData>
@@ -41786,7 +44537,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F2DC46C-13BF-4206-9D00-887894ECFD69}">
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -48605,6 +51356,461 @@
       </c>
       <c r="U121">
         <v>5.7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <v>263.72000000000003</v>
+      </c>
+      <c r="C122">
+        <v>60.3</v>
+      </c>
+      <c r="D122">
+        <v>52.7</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>347.69</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>3.3</v>
+      </c>
+      <c r="J122">
+        <v>48.1</v>
+      </c>
+      <c r="K122">
+        <v>136.6</v>
+      </c>
+      <c r="L122">
+        <v>614.66999999999996</v>
+      </c>
+      <c r="M122">
+        <v>829.56000000000006</v>
+      </c>
+      <c r="N122">
+        <v>3.6</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>76.3</v>
+      </c>
+      <c r="Q122">
+        <v>130.43</v>
+      </c>
+      <c r="R122">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S122">
+        <v>1227.05</v>
+      </c>
+      <c r="T122">
+        <v>1689.17</v>
+      </c>
+      <c r="U122">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <v>340.79</v>
+      </c>
+      <c r="C123">
+        <v>59.7</v>
+      </c>
+      <c r="D123">
+        <v>102.7</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>288.64</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>3.1</v>
+      </c>
+      <c r="J123">
+        <v>30.3</v>
+      </c>
+      <c r="K123">
+        <v>168.6</v>
+      </c>
+      <c r="L123">
+        <v>650.04000000000008</v>
+      </c>
+      <c r="M123">
+        <v>555.74</v>
+      </c>
+      <c r="N123">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>71.3</v>
+      </c>
+      <c r="Q123">
+        <v>138.30000000000001</v>
+      </c>
+      <c r="R123">
+        <v>2.1</v>
+      </c>
+      <c r="S123">
+        <v>1408.94</v>
+      </c>
+      <c r="T123">
+        <v>1721.94</v>
+      </c>
+      <c r="U123">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <v>447.27</v>
+      </c>
+      <c r="C124">
+        <v>131.5</v>
+      </c>
+      <c r="D124">
+        <v>170.6</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>272.95</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0.7</v>
+      </c>
+      <c r="J124">
+        <v>25.1</v>
+      </c>
+      <c r="K124">
+        <v>232.8</v>
+      </c>
+      <c r="L124">
+        <v>879.30000000000007</v>
+      </c>
+      <c r="M124">
+        <v>195.42</v>
+      </c>
+      <c r="N124">
+        <v>3.7</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>94.9</v>
+      </c>
+      <c r="Q124">
+        <v>208.34</v>
+      </c>
+      <c r="R124">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S124">
+        <v>1867.97</v>
+      </c>
+      <c r="T124">
+        <v>1684</v>
+      </c>
+      <c r="U124">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <v>467.44</v>
+      </c>
+      <c r="C125">
+        <v>97.9</v>
+      </c>
+      <c r="D125">
+        <v>35.4</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>274.81000000000012</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>29.7</v>
+      </c>
+      <c r="K125">
+        <v>213.8</v>
+      </c>
+      <c r="L125">
+        <v>1052.23</v>
+      </c>
+      <c r="M125">
+        <v>85.87</v>
+      </c>
+      <c r="N125">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>112.6</v>
+      </c>
+      <c r="Q125">
+        <v>165.61</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+      <c r="S125">
+        <v>1494.22</v>
+      </c>
+      <c r="T125">
+        <v>1852.75</v>
+      </c>
+      <c r="U125">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <v>306.14</v>
+      </c>
+      <c r="C126">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D126">
+        <v>11.8</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>287.10000000000002</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J126">
+        <v>13.3</v>
+      </c>
+      <c r="K126">
+        <v>223.4</v>
+      </c>
+      <c r="L126">
+        <v>1181.78</v>
+      </c>
+      <c r="M126">
+        <v>116.23</v>
+      </c>
+      <c r="N126">
+        <v>3.2</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>147.4</v>
+      </c>
+      <c r="Q126">
+        <v>174.63</v>
+      </c>
+      <c r="R126">
+        <v>1.3</v>
+      </c>
+      <c r="S126">
+        <v>1512.88</v>
+      </c>
+      <c r="T126">
+        <v>1591.07</v>
+      </c>
+      <c r="U126">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <v>694.22</v>
+      </c>
+      <c r="C127">
+        <v>127.5</v>
+      </c>
+      <c r="D127">
+        <v>38</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>368.67</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0.9</v>
+      </c>
+      <c r="J127">
+        <v>83.199999999999989</v>
+      </c>
+      <c r="K127">
+        <v>180.1</v>
+      </c>
+      <c r="L127">
+        <v>1087.3699999999999</v>
+      </c>
+      <c r="M127">
+        <v>195.09</v>
+      </c>
+      <c r="N127">
+        <v>3</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>30.5</v>
+      </c>
+      <c r="Q127">
+        <v>590.36</v>
+      </c>
+      <c r="R127">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S127">
+        <v>1586.88</v>
+      </c>
+      <c r="T127">
+        <v>1441.53</v>
+      </c>
+      <c r="U127">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <v>803.75</v>
+      </c>
+      <c r="C128">
+        <v>41.1</v>
+      </c>
+      <c r="D128">
+        <v>26.9</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>268.94</v>
+      </c>
+      <c r="G128">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0.8</v>
+      </c>
+      <c r="J128">
+        <v>5</v>
+      </c>
+      <c r="K128">
+        <v>166.6</v>
+      </c>
+      <c r="L128">
+        <v>842.57999999999993</v>
+      </c>
+      <c r="M128">
+        <v>183.42</v>
+      </c>
+      <c r="N128">
+        <v>3.2</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>23.4</v>
+      </c>
+      <c r="Q128">
+        <v>195.49</v>
+      </c>
+      <c r="R128">
+        <v>2.6</v>
+      </c>
+      <c r="S128">
+        <v>1529.18</v>
+      </c>
+      <c r="T128">
+        <v>2780.05</v>
+      </c>
+      <c r="U128">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -48614,7 +51820,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323B3241-5DFF-4ED4-9FDD-8FF0AE18E1CD}">
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -55435,6 +58641,461 @@
         <v>19576.8</v>
       </c>
     </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <v>54329</v>
+      </c>
+      <c r="C122">
+        <v>20148.599999999999</v>
+      </c>
+      <c r="D122">
+        <v>41510.5</v>
+      </c>
+      <c r="E122">
+        <v>4789.5</v>
+      </c>
+      <c r="F122">
+        <v>2154.3000000000002</v>
+      </c>
+      <c r="G122">
+        <v>14.9</v>
+      </c>
+      <c r="H122">
+        <v>0.2</v>
+      </c>
+      <c r="I122">
+        <v>15993</v>
+      </c>
+      <c r="J122">
+        <v>4617.8999999999996</v>
+      </c>
+      <c r="K122">
+        <v>8763.4</v>
+      </c>
+      <c r="L122">
+        <v>50601.1</v>
+      </c>
+      <c r="M122">
+        <v>33270.699999999997</v>
+      </c>
+      <c r="N122">
+        <v>259</v>
+      </c>
+      <c r="O122">
+        <v>30.2</v>
+      </c>
+      <c r="P122">
+        <v>2149</v>
+      </c>
+      <c r="Q122">
+        <v>25193.8</v>
+      </c>
+      <c r="R122">
+        <v>1621.8</v>
+      </c>
+      <c r="S122">
+        <v>15255.1</v>
+      </c>
+      <c r="T122">
+        <v>47327</v>
+      </c>
+      <c r="U122">
+        <v>18830.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <v>45131.6</v>
+      </c>
+      <c r="C123">
+        <v>17195.099999999999</v>
+      </c>
+      <c r="D123">
+        <v>38920.1</v>
+      </c>
+      <c r="E123">
+        <v>4333.3999999999996</v>
+      </c>
+      <c r="F123">
+        <v>2920.8</v>
+      </c>
+      <c r="G123">
+        <v>14.9</v>
+      </c>
+      <c r="H123">
+        <v>0.1</v>
+      </c>
+      <c r="I123">
+        <v>15508.6</v>
+      </c>
+      <c r="J123">
+        <v>4184.3999999999996</v>
+      </c>
+      <c r="K123">
+        <v>10359.5</v>
+      </c>
+      <c r="L123">
+        <v>41905.599999999999</v>
+      </c>
+      <c r="M123">
+        <v>25198</v>
+      </c>
+      <c r="N123">
+        <v>356.7</v>
+      </c>
+      <c r="O123">
+        <v>25.9</v>
+      </c>
+      <c r="P123">
+        <v>3322.2</v>
+      </c>
+      <c r="Q123">
+        <v>28661.9</v>
+      </c>
+      <c r="R123">
+        <v>1907.1</v>
+      </c>
+      <c r="S123">
+        <v>13505.1</v>
+      </c>
+      <c r="T123">
+        <v>44265.4</v>
+      </c>
+      <c r="U123">
+        <v>16545.599999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <v>60384.800000000003</v>
+      </c>
+      <c r="C124">
+        <v>19281.599999999999</v>
+      </c>
+      <c r="D124">
+        <v>41024.699999999997</v>
+      </c>
+      <c r="E124">
+        <v>4701.3</v>
+      </c>
+      <c r="F124">
+        <v>3721</v>
+      </c>
+      <c r="G124">
+        <v>14.7</v>
+      </c>
+      <c r="H124">
+        <v>0.1</v>
+      </c>
+      <c r="I124">
+        <v>19010</v>
+      </c>
+      <c r="J124">
+        <v>6278</v>
+      </c>
+      <c r="K124">
+        <v>10459.200000000001</v>
+      </c>
+      <c r="L124">
+        <v>46816.9</v>
+      </c>
+      <c r="M124">
+        <v>28343.3</v>
+      </c>
+      <c r="N124">
+        <v>427.2</v>
+      </c>
+      <c r="O124">
+        <v>37.9</v>
+      </c>
+      <c r="P124">
+        <v>4423.2</v>
+      </c>
+      <c r="Q124">
+        <v>27089.7</v>
+      </c>
+      <c r="R124">
+        <v>2712.3</v>
+      </c>
+      <c r="S124">
+        <v>14773.7</v>
+      </c>
+      <c r="T124">
+        <v>49073</v>
+      </c>
+      <c r="U124">
+        <v>21272.400000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <v>53061.5</v>
+      </c>
+      <c r="C125">
+        <v>19471.900000000001</v>
+      </c>
+      <c r="D125">
+        <v>40330.800000000003</v>
+      </c>
+      <c r="E125">
+        <v>4444.1000000000004</v>
+      </c>
+      <c r="F125">
+        <v>4525.3</v>
+      </c>
+      <c r="G125">
+        <v>14.5</v>
+      </c>
+      <c r="H125">
+        <v>0.3</v>
+      </c>
+      <c r="I125">
+        <v>18345.7</v>
+      </c>
+      <c r="J125">
+        <v>6696</v>
+      </c>
+      <c r="K125">
+        <v>11136.5</v>
+      </c>
+      <c r="L125">
+        <v>54373.400000000009</v>
+      </c>
+      <c r="M125">
+        <v>34878.5</v>
+      </c>
+      <c r="N125">
+        <v>681.7</v>
+      </c>
+      <c r="O125">
+        <v>52.2</v>
+      </c>
+      <c r="P125">
+        <v>5159.2</v>
+      </c>
+      <c r="Q125">
+        <v>29787.1</v>
+      </c>
+      <c r="R125">
+        <v>2117.5</v>
+      </c>
+      <c r="S125">
+        <v>16632.7</v>
+      </c>
+      <c r="T125">
+        <v>52808.800000000003</v>
+      </c>
+      <c r="U125">
+        <v>23757.1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <v>62239.8</v>
+      </c>
+      <c r="C126">
+        <v>19921.5</v>
+      </c>
+      <c r="D126">
+        <v>42775.499999999993</v>
+      </c>
+      <c r="E126">
+        <v>4447.7</v>
+      </c>
+      <c r="F126">
+        <v>6128.1</v>
+      </c>
+      <c r="G126">
+        <v>14.3</v>
+      </c>
+      <c r="H126">
+        <v>0.1</v>
+      </c>
+      <c r="I126">
+        <v>20423.900000000001</v>
+      </c>
+      <c r="J126">
+        <v>6999.2</v>
+      </c>
+      <c r="K126">
+        <v>10509</v>
+      </c>
+      <c r="L126">
+        <v>54243.7</v>
+      </c>
+      <c r="M126">
+        <v>35445.300000000003</v>
+      </c>
+      <c r="N126">
+        <v>737.5</v>
+      </c>
+      <c r="O126">
+        <v>54.3</v>
+      </c>
+      <c r="P126">
+        <v>5802.4</v>
+      </c>
+      <c r="Q126">
+        <v>27042.1</v>
+      </c>
+      <c r="R126">
+        <v>2241.9</v>
+      </c>
+      <c r="S126">
+        <v>16201</v>
+      </c>
+      <c r="T126">
+        <v>57261.1</v>
+      </c>
+      <c r="U126">
+        <v>25319.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <v>61806.399999999987</v>
+      </c>
+      <c r="C127">
+        <v>19866.599999999999</v>
+      </c>
+      <c r="D127">
+        <v>38080.099999999991</v>
+      </c>
+      <c r="E127">
+        <v>4083.3</v>
+      </c>
+      <c r="F127">
+        <v>6290.9</v>
+      </c>
+      <c r="G127">
+        <v>14.2</v>
+      </c>
+      <c r="H127">
+        <v>0.3</v>
+      </c>
+      <c r="I127">
+        <v>20916.3</v>
+      </c>
+      <c r="J127">
+        <v>10690.5</v>
+      </c>
+      <c r="K127">
+        <v>13037.6</v>
+      </c>
+      <c r="L127">
+        <v>56042.2</v>
+      </c>
+      <c r="M127">
+        <v>33353.5</v>
+      </c>
+      <c r="N127">
+        <v>837.80000000000007</v>
+      </c>
+      <c r="O127">
+        <v>88</v>
+      </c>
+      <c r="P127">
+        <v>6556.6</v>
+      </c>
+      <c r="Q127">
+        <v>28008.799999999999</v>
+      </c>
+      <c r="R127">
+        <v>4710.8</v>
+      </c>
+      <c r="S127">
+        <v>16699.599999999999</v>
+      </c>
+      <c r="T127">
+        <v>59281.5</v>
+      </c>
+      <c r="U127">
+        <v>27352.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <v>62214.8</v>
+      </c>
+      <c r="C128">
+        <v>21013.7</v>
+      </c>
+      <c r="D128">
+        <v>34238.1</v>
+      </c>
+      <c r="E128">
+        <v>3883.1</v>
+      </c>
+      <c r="F128">
+        <v>6076.4000000000005</v>
+      </c>
+      <c r="G128">
+        <v>14</v>
+      </c>
+      <c r="H128">
+        <v>0.2</v>
+      </c>
+      <c r="I128">
+        <v>21832</v>
+      </c>
+      <c r="J128">
+        <v>13810</v>
+      </c>
+      <c r="K128">
+        <v>11245.8</v>
+      </c>
+      <c r="L128">
+        <v>54984.800000000003</v>
+      </c>
+      <c r="M128">
+        <v>32197.3</v>
+      </c>
+      <c r="N128">
+        <v>808.9</v>
+      </c>
+      <c r="O128">
+        <v>87.8</v>
+      </c>
+      <c r="P128">
+        <v>7458.2</v>
+      </c>
+      <c r="Q128">
+        <v>27987.200000000001</v>
+      </c>
+      <c r="R128">
+        <v>2247.1</v>
+      </c>
+      <c r="S128">
+        <v>18734.2</v>
+      </c>
+      <c r="T128">
+        <v>63008.600000000013</v>
+      </c>
+      <c r="U128">
+        <v>23460.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
